--- a/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10ABA9D9-BDA1-9E40-8A0C-4C42C64D9CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF832185-8BD5-5C4A-AA1F-A5899177FEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17980" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14280" windowHeight="17980" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="49">
   <si>
     <t>winter_barley_59</t>
   </si>
@@ -156,19 +156,59 @@
   </si>
   <si>
     <t>nan</t>
+  </si>
+  <si>
+    <t>cyb</t>
+  </si>
+  <si>
+    <t>cya</t>
+  </si>
+  <si>
+    <t>winter_barley_60</t>
+  </si>
+  <si>
+    <t>winter_barley_61</t>
+  </si>
+  <si>
+    <t>winter_barley_62</t>
+  </si>
+  <si>
+    <t>spring_barley_63</t>
+  </si>
+  <si>
+    <t>spring_barley_64</t>
+  </si>
+  <si>
+    <t>spring_barley_66</t>
+  </si>
+  <si>
+    <t>spring_barley_65</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF030712"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -191,8 +231,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,237 +570,1086 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9258CFFF-D0F8-3E49-9200-AC8FAB870EFD}">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C2">
-        <v>0.2</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="3">
         <v>2.5</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>35</v>
+      </c>
+      <c r="H2" s="3">
+        <v>105</v>
+      </c>
+      <c r="I2" s="3">
         <v>140</v>
       </c>
-      <c r="H2">
+      <c r="J2" s="3">
+        <v>90</v>
+      </c>
+      <c r="K2" s="3">
+        <v>240</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N2" s="3">
+        <v>1</v>
+      </c>
+      <c r="O2" s="3">
+        <v>15</v>
+      </c>
+      <c r="P2" s="3">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>25</v>
+      </c>
+      <c r="R2" s="3">
+        <v>20</v>
+      </c>
+      <c r="S2" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="T2" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U2" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>40</v>
+      </c>
+      <c r="H3" s="3">
         <v>120</v>
       </c>
-      <c r="I2">
+      <c r="I3" s="3">
+        <v>160</v>
+      </c>
+      <c r="J3" s="3">
+        <v>90</v>
+      </c>
+      <c r="K3" s="3">
+        <v>240</v>
+      </c>
+      <c r="L3" s="3">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N3" s="3">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3">
+        <v>15</v>
+      </c>
+      <c r="P3" s="3">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>25</v>
+      </c>
+      <c r="R3" s="3">
+        <v>20</v>
+      </c>
+      <c r="S3" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="T3" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U3" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>45</v>
+      </c>
+      <c r="H4" s="3">
+        <v>135</v>
+      </c>
+      <c r="I4" s="3">
+        <v>180</v>
+      </c>
+      <c r="J4" s="3">
+        <v>90</v>
+      </c>
+      <c r="K4" s="3">
+        <v>240</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N4" s="3">
+        <v>1</v>
+      </c>
+      <c r="O4" s="3">
+        <v>15</v>
+      </c>
+      <c r="P4" s="3">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>25</v>
+      </c>
+      <c r="R4" s="3">
+        <v>20</v>
+      </c>
+      <c r="S4" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="T4" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U4" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>50</v>
+      </c>
+      <c r="H5" s="3">
         <v>150</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
+      <c r="I5" s="3">
+        <v>200</v>
+      </c>
+      <c r="J5" s="3">
+        <v>90</v>
+      </c>
+      <c r="K5" s="3">
+        <v>240</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="3">
+        <v>1</v>
+      </c>
+      <c r="O5" s="3">
         <v>15</v>
       </c>
-      <c r="N2">
+      <c r="P5" s="3">
         <v>30</v>
       </c>
-      <c r="O2">
+      <c r="Q5" s="3">
         <v>25</v>
       </c>
-      <c r="P2">
+      <c r="R5" s="3">
         <v>20</v>
       </c>
-      <c r="Q2">
+      <c r="S5" s="3">
         <v>0.4</v>
       </c>
-      <c r="R2">
+      <c r="T5" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="S2">
+      <c r="U5" s="3">
         <v>0.25</v>
       </c>
-      <c r="T2">
+      <c r="V5" s="3">
         <v>0.85</v>
       </c>
-      <c r="U2">
-        <v>0.2</v>
-      </c>
-      <c r="V2">
+      <c r="W5" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="X5" s="3">
         <v>0.4</v>
       </c>
-      <c r="W2">
+      <c r="Y5" s="3">
         <v>0.6</v>
       </c>
-      <c r="X2">
-        <v>0.2</v>
-      </c>
-      <c r="Y2">
+      <c r="Z5" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AA5" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
+      <c r="AB5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="3">
         <v>5</v>
       </c>
-      <c r="AB2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>39</v>
-      </c>
+      <c r="AD5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM5" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>90</v>
+      </c>
+      <c r="J6" s="3">
+        <v>90</v>
+      </c>
+      <c r="K6" s="3">
+        <v>240</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N6" s="3">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2">
+        <v>15</v>
+      </c>
+      <c r="P6">
+        <v>25</v>
+      </c>
+      <c r="Q6">
+        <v>40</v>
+      </c>
+      <c r="R6" s="2">
+        <v>20</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T6" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM6" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>105</v>
+      </c>
+      <c r="J7" s="3">
+        <v>90</v>
+      </c>
+      <c r="K7" s="3">
+        <v>240</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N7" s="3">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2">
+        <v>15</v>
+      </c>
+      <c r="P7">
+        <v>25</v>
+      </c>
+      <c r="Q7">
+        <v>40</v>
+      </c>
+      <c r="R7" s="2">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T7" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM7" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>120</v>
+      </c>
+      <c r="J8" s="3">
+        <v>90</v>
+      </c>
+      <c r="K8" s="3">
+        <v>240</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N8" s="3">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2">
+        <v>15</v>
+      </c>
+      <c r="P8">
+        <v>25</v>
+      </c>
+      <c r="Q8">
+        <v>40</v>
+      </c>
+      <c r="R8" s="2">
+        <v>20</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T8" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM8" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>135</v>
+      </c>
+      <c r="J9" s="3">
+        <v>90</v>
+      </c>
+      <c r="K9" s="3">
+        <v>240</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2">
+        <v>15</v>
+      </c>
+      <c r="P9">
+        <v>25</v>
+      </c>
+      <c r="Q9">
+        <v>40</v>
+      </c>
+      <c r="R9" s="2">
+        <v>20</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T9" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM9" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="G10" s="3"/>
+      <c r="H10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF832185-8BD5-5C4A-AA1F-A5899177FEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CE0B29-8E1F-B549-83F4-159C82A5ABD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="14280" windowHeight="17980" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="10740" windowHeight="16340" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="58">
   <si>
     <t>winter_barley_59</t>
   </si>
@@ -183,6 +183,33 @@
   </si>
   <si>
     <t>spring_barley_65</t>
+  </si>
+  <si>
+    <t>winter_wheat_1</t>
+  </si>
+  <si>
+    <t>winter_wheat_2</t>
+  </si>
+  <si>
+    <t>winter_wheat_3</t>
+  </si>
+  <si>
+    <t>winter_wheat_4</t>
+  </si>
+  <si>
+    <t>spring_wheat_5</t>
+  </si>
+  <si>
+    <t>spring_wheat_6</t>
+  </si>
+  <si>
+    <t>spring_wheat_7</t>
+  </si>
+  <si>
+    <t>spring_wheat_8</t>
+  </si>
+  <si>
+    <t>spring_wheat_9</t>
   </si>
 </sst>
 </file>
@@ -231,11 +258,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,648 +596,648 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9258CFFF-D0F8-3E49-9200-AC8FAB870EFD}">
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AM18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2">
+        <v>0.2</v>
+      </c>
+      <c r="D2">
         <v>2.5</v>
       </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>35</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2">
         <v>105</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2">
         <v>140</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2">
         <v>90</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2">
         <v>240</v>
       </c>
-      <c r="L2" s="3">
-        <v>1</v>
-      </c>
-      <c r="M2" s="3">
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
         <v>1.5</v>
       </c>
-      <c r="N2" s="3">
-        <v>1</v>
-      </c>
-      <c r="O2" s="3">
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
         <v>15</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2">
         <v>30</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2">
         <v>25</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2">
         <v>20</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2">
         <v>0.4</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="U2" s="3">
+      <c r="U2">
         <v>0.25</v>
       </c>
-      <c r="V2" s="3">
+      <c r="V2">
         <v>0.85</v>
       </c>
-      <c r="W2" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="X2" s="3">
+      <c r="W2">
+        <v>0.2</v>
+      </c>
+      <c r="X2">
         <v>0.4</v>
       </c>
-      <c r="Y2" s="3">
+      <c r="Y2">
         <v>0.6</v>
       </c>
-      <c r="Z2" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="AA2" s="3">
+      <c r="Z2">
+        <v>0.2</v>
+      </c>
+      <c r="AA2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AB2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="3">
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <v>5</v>
       </c>
-      <c r="AD2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM2" s="3" t="s">
+      <c r="AD2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3">
+        <v>0.2</v>
+      </c>
+      <c r="D3">
         <v>2.5</v>
       </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>40</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <v>120</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3">
         <v>160</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3">
         <v>90</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3">
         <v>240</v>
       </c>
-      <c r="L3" s="3">
-        <v>1</v>
-      </c>
-      <c r="M3" s="3">
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1.5</v>
       </c>
-      <c r="N3" s="3">
-        <v>1</v>
-      </c>
-      <c r="O3" s="3">
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
         <v>15</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3">
         <v>30</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3">
         <v>25</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3">
         <v>20</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3">
         <v>0.4</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3">
         <v>0.25</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V3">
         <v>0.85</v>
       </c>
-      <c r="W3" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="X3" s="3">
+      <c r="W3">
+        <v>0.2</v>
+      </c>
+      <c r="X3">
         <v>0.4</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="Y3">
         <v>0.6</v>
       </c>
-      <c r="Z3" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="AA3" s="3">
+      <c r="Z3">
+        <v>0.2</v>
+      </c>
+      <c r="AA3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AB3" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="3">
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <v>5</v>
       </c>
-      <c r="AD3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AD3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4">
+        <v>0.2</v>
+      </c>
+      <c r="D4">
         <v>2.5</v>
       </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>45</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>135</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4">
         <v>180</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4">
         <v>90</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4">
         <v>240</v>
       </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-      <c r="M4" s="3">
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1.5</v>
       </c>
-      <c r="N4" s="3">
-        <v>1</v>
-      </c>
-      <c r="O4" s="3">
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
         <v>15</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4">
         <v>30</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4">
         <v>25</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4">
         <v>20</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4">
         <v>0.4</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4">
         <v>1.1499999999999999</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4">
         <v>0.25</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V4">
         <v>0.85</v>
       </c>
-      <c r="W4" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="X4" s="3">
+      <c r="W4">
+        <v>0.2</v>
+      </c>
+      <c r="X4">
         <v>0.4</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y4">
         <v>0.6</v>
       </c>
-      <c r="Z4" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="AA4" s="3">
+      <c r="Z4">
+        <v>0.2</v>
+      </c>
+      <c r="AA4">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AB4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="3">
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
         <v>5</v>
       </c>
-      <c r="AD4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM4" s="3" t="s">
+      <c r="AD4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C5">
+        <v>0.2</v>
+      </c>
+      <c r="D5">
         <v>2.5</v>
       </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>50</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>150</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5">
         <v>200</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5">
         <v>90</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5">
         <v>240</v>
       </c>
-      <c r="L5" s="3">
-        <v>1</v>
-      </c>
-      <c r="M5" s="3">
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1.5</v>
       </c>
-      <c r="N5" s="3">
-        <v>1</v>
-      </c>
-      <c r="O5" s="3">
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
         <v>15</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5">
         <v>30</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5">
         <v>25</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5">
         <v>20</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5">
         <v>0.4</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5">
         <v>1.1499999999999999</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5">
         <v>0.25</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5">
         <v>0.85</v>
       </c>
-      <c r="W5" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="X5" s="3">
+      <c r="W5">
+        <v>0.2</v>
+      </c>
+      <c r="X5">
         <v>0.4</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5">
         <v>0.6</v>
       </c>
-      <c r="Z5" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="AA5" s="3">
+      <c r="Z5">
+        <v>0.2</v>
+      </c>
+      <c r="AA5">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AB5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="3">
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
         <v>5</v>
       </c>
-      <c r="AD5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM5" s="3" t="s">
+      <c r="AD5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>0.15</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>90</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6">
         <v>90</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6">
         <v>240</v>
       </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1.5</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6">
         <v>1</v>
       </c>
       <c r="O6" s="2">
@@ -1253,84 +1279,84 @@
       <c r="AA6" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AB6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="3">
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
         <v>5</v>
       </c>
-      <c r="AD6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM6" s="3" t="s">
+      <c r="AD6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>0.15</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7">
         <v>105</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7">
         <v>90</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7">
         <v>240</v>
       </c>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-      <c r="M7" s="3">
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
         <v>1.5</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7">
         <v>1</v>
       </c>
       <c r="O7" s="2">
@@ -1372,84 +1398,84 @@
       <c r="AA7" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AB7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="3">
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
         <v>5</v>
       </c>
-      <c r="AD7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM7" s="3" t="s">
+      <c r="AD7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>0.15</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8">
         <v>120</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8">
         <v>90</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8">
         <v>240</v>
       </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
         <v>1.5</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8">
         <v>1</v>
       </c>
       <c r="O8" s="2">
@@ -1491,84 +1517,84 @@
       <c r="AA8" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
         <v>5</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM8" s="3" t="s">
+      <c r="AD8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>0.15</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9">
         <v>2</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9">
         <v>135</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9">
         <v>90</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9">
         <v>240</v>
       </c>
-      <c r="L9" s="3">
-        <v>1</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
         <v>1.5</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9">
         <v>1</v>
       </c>
       <c r="O9" s="2">
@@ -1610,46 +1636,1113 @@
       <c r="AA9" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AB9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
         <v>5</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM9" s="3" t="s">
+      <c r="AD9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="G10" s="3"/>
-      <c r="H10" s="1"/>
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>35</v>
+      </c>
+      <c r="H10">
+        <v>105</v>
+      </c>
+      <c r="I10">
+        <v>140</v>
+      </c>
+      <c r="J10">
+        <v>90</v>
+      </c>
+      <c r="K10">
+        <v>200</v>
+      </c>
+      <c r="L10">
+        <v>1.5</v>
+      </c>
+      <c r="M10">
+        <v>1.8</v>
+      </c>
+      <c r="N10">
+        <v>1.2</v>
+      </c>
+      <c r="O10" s="2">
+        <v>15</v>
+      </c>
+      <c r="P10">
+        <v>30</v>
+      </c>
+      <c r="Q10">
+        <v>35</v>
+      </c>
+      <c r="R10" s="2">
+        <v>20</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T10" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>5</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11">
+        <v>0.2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>40</v>
+      </c>
+      <c r="H11">
+        <v>120</v>
+      </c>
+      <c r="I11">
+        <v>160</v>
+      </c>
+      <c r="J11">
+        <v>90</v>
+      </c>
+      <c r="K11">
+        <v>200</v>
+      </c>
+      <c r="L11">
+        <v>1.5</v>
+      </c>
+      <c r="M11">
+        <v>1.8</v>
+      </c>
+      <c r="N11">
+        <v>1.2</v>
+      </c>
+      <c r="O11" s="2">
+        <v>15</v>
+      </c>
+      <c r="P11">
+        <v>30</v>
+      </c>
+      <c r="Q11">
+        <v>35</v>
+      </c>
+      <c r="R11" s="2">
+        <v>20</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T11" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>5</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>0.2</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>45</v>
+      </c>
+      <c r="H12">
+        <v>135</v>
+      </c>
+      <c r="I12">
+        <v>180</v>
+      </c>
+      <c r="J12">
+        <v>90</v>
+      </c>
+      <c r="K12">
+        <v>200</v>
+      </c>
+      <c r="L12">
+        <v>1.5</v>
+      </c>
+      <c r="M12">
+        <v>1.8</v>
+      </c>
+      <c r="N12">
+        <v>1.2</v>
+      </c>
+      <c r="O12" s="2">
+        <v>15</v>
+      </c>
+      <c r="P12">
+        <v>30</v>
+      </c>
+      <c r="Q12">
+        <v>35</v>
+      </c>
+      <c r="R12" s="2">
+        <v>20</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T12" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>5</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13">
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>50</v>
+      </c>
+      <c r="H13">
+        <v>150</v>
+      </c>
+      <c r="I13">
+        <v>200</v>
+      </c>
+      <c r="J13">
+        <v>90</v>
+      </c>
+      <c r="K13">
+        <v>200</v>
+      </c>
+      <c r="L13">
+        <v>1.5</v>
+      </c>
+      <c r="M13">
+        <v>1.8</v>
+      </c>
+      <c r="N13">
+        <v>1.2</v>
+      </c>
+      <c r="O13" s="2">
+        <v>15</v>
+      </c>
+      <c r="P13">
+        <v>30</v>
+      </c>
+      <c r="Q13">
+        <v>35</v>
+      </c>
+      <c r="R13" s="2">
+        <v>20</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T13" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>5</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14">
+        <v>0.15</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>90</v>
+      </c>
+      <c r="J14">
+        <v>90</v>
+      </c>
+      <c r="K14">
+        <v>200</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1.5</v>
+      </c>
+      <c r="N14">
+        <v>1.2</v>
+      </c>
+      <c r="O14" s="2">
+        <v>15</v>
+      </c>
+      <c r="P14">
+        <v>25</v>
+      </c>
+      <c r="Q14">
+        <v>40</v>
+      </c>
+      <c r="R14" s="2">
+        <v>20</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T14" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>5</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <v>0.15</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>105</v>
+      </c>
+      <c r="J15">
+        <v>90</v>
+      </c>
+      <c r="K15">
+        <v>200</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1.5</v>
+      </c>
+      <c r="N15">
+        <v>1.2</v>
+      </c>
+      <c r="O15" s="2">
+        <v>15</v>
+      </c>
+      <c r="P15">
+        <v>25</v>
+      </c>
+      <c r="Q15">
+        <v>40</v>
+      </c>
+      <c r="R15" s="2">
+        <v>20</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T15" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>5</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16">
+        <v>0.15</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>120</v>
+      </c>
+      <c r="J16">
+        <v>90</v>
+      </c>
+      <c r="K16">
+        <v>200</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1.5</v>
+      </c>
+      <c r="N16">
+        <v>1.2</v>
+      </c>
+      <c r="O16" s="2">
+        <v>15</v>
+      </c>
+      <c r="P16">
+        <v>25</v>
+      </c>
+      <c r="Q16">
+        <v>40</v>
+      </c>
+      <c r="R16" s="2">
+        <v>20</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T16" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V16" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>5</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17">
+        <v>0.15</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>135</v>
+      </c>
+      <c r="J17">
+        <v>90</v>
+      </c>
+      <c r="K17">
+        <v>200</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1.5</v>
+      </c>
+      <c r="N17">
+        <v>1.2</v>
+      </c>
+      <c r="O17" s="2">
+        <v>15</v>
+      </c>
+      <c r="P17">
+        <v>25</v>
+      </c>
+      <c r="Q17">
+        <v>40</v>
+      </c>
+      <c r="R17" s="2">
+        <v>20</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T17" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>5</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18">
+        <v>0.15</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>150</v>
+      </c>
+      <c r="J18">
+        <v>90</v>
+      </c>
+      <c r="K18">
+        <v>200</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1.5</v>
+      </c>
+      <c r="N18">
+        <v>1.2</v>
+      </c>
+      <c r="O18" s="2">
+        <v>15</v>
+      </c>
+      <c r="P18">
+        <v>25</v>
+      </c>
+      <c r="Q18">
+        <v>40</v>
+      </c>
+      <c r="R18" s="2">
+        <v>20</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T18" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>5</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CE0B29-8E1F-B549-83F4-159C82A5ABD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6E57C8-E44E-0D40-94F9-4930F2CD4737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="10740" windowHeight="16340" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="10000" windowHeight="16340" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="71">
   <si>
     <t>winter_barley_59</t>
   </si>
@@ -210,13 +210,52 @@
   </si>
   <si>
     <t>spring_wheat_9</t>
+  </si>
+  <si>
+    <t>silage_maize_53</t>
+  </si>
+  <si>
+    <t>silage_maize_54</t>
+  </si>
+  <si>
+    <t>silage_maize_55</t>
+  </si>
+  <si>
+    <t>silage_maize_56</t>
+  </si>
+  <si>
+    <t>silage_maize_57</t>
+  </si>
+  <si>
+    <t>silage_maize_58</t>
+  </si>
+  <si>
+    <t>white_potato_135</t>
+  </si>
+  <si>
+    <t>white_potato_136</t>
+  </si>
+  <si>
+    <t>white_potato_137</t>
+  </si>
+  <si>
+    <t>white_potato_138</t>
+  </si>
+  <si>
+    <t>white_potato_139</t>
+  </si>
+  <si>
+    <t>white_potato_140</t>
+  </si>
+  <si>
+    <t>white_potato_141</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -236,6 +275,12 @@
       <color rgb="FF030712"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -596,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9258CFFF-D0F8-3E49-9200-AC8FAB870EFD}">
-  <dimension ref="A1:AM18"/>
+  <dimension ref="A1:AM31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -2744,7 +2789,1555 @@
         <v>39</v>
       </c>
     </row>
+    <row r="19" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19">
+        <v>0.4</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>105</v>
+      </c>
+      <c r="J19">
+        <v>65</v>
+      </c>
+      <c r="K19">
+        <v>365</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1.7</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19" s="2">
+        <v>20</v>
+      </c>
+      <c r="P19">
+        <v>35</v>
+      </c>
+      <c r="Q19">
+        <v>35</v>
+      </c>
+      <c r="R19" s="2">
+        <v>10</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T19" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U19" s="2">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="W19" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>10</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20">
+        <v>0.4</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>120</v>
+      </c>
+      <c r="J20">
+        <v>65</v>
+      </c>
+      <c r="K20">
+        <v>365</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1.7</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+      <c r="O20" s="2">
+        <v>20</v>
+      </c>
+      <c r="P20">
+        <v>35</v>
+      </c>
+      <c r="Q20">
+        <v>35</v>
+      </c>
+      <c r="R20" s="2">
+        <v>10</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T20" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U20" s="2">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="W20" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>10</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21">
+        <v>0.45</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>135</v>
+      </c>
+      <c r="J21">
+        <v>65</v>
+      </c>
+      <c r="K21">
+        <v>365</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1.7</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21" s="2">
+        <v>20</v>
+      </c>
+      <c r="P21">
+        <v>35</v>
+      </c>
+      <c r="Q21">
+        <v>35</v>
+      </c>
+      <c r="R21" s="2">
+        <v>10</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T21" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U21" s="2">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="W21" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>10</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22">
+        <v>0.45</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>150</v>
+      </c>
+      <c r="J22">
+        <v>65</v>
+      </c>
+      <c r="K22">
+        <v>365</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1.7</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+      <c r="O22" s="2">
+        <v>20</v>
+      </c>
+      <c r="P22">
+        <v>35</v>
+      </c>
+      <c r="Q22">
+        <v>35</v>
+      </c>
+      <c r="R22" s="2">
+        <v>10</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T22" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U22" s="2">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="W22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>10</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23">
+        <v>0.45</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>165</v>
+      </c>
+      <c r="J23">
+        <v>65</v>
+      </c>
+      <c r="K23">
+        <v>365</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1.7</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23" s="2">
+        <v>20</v>
+      </c>
+      <c r="P23">
+        <v>35</v>
+      </c>
+      <c r="Q23">
+        <v>35</v>
+      </c>
+      <c r="R23" s="2">
+        <v>10</v>
+      </c>
+      <c r="S23" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T23" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U23" s="2">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="W23" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="X23" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z23" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>10</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24">
+        <v>0.45</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>180</v>
+      </c>
+      <c r="J24">
+        <v>65</v>
+      </c>
+      <c r="K24">
+        <v>365</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1.7</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24" s="2">
+        <v>20</v>
+      </c>
+      <c r="P24">
+        <v>35</v>
+      </c>
+      <c r="Q24">
+        <v>35</v>
+      </c>
+      <c r="R24" s="2">
+        <v>10</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T24" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U24" s="2">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="W24" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="X24" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA24" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>10</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25">
+        <v>0.3</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>90</v>
+      </c>
+      <c r="J25">
+        <v>90</v>
+      </c>
+      <c r="K25">
+        <v>180</v>
+      </c>
+      <c r="L25">
+        <v>0.4</v>
+      </c>
+      <c r="M25">
+        <v>0.6</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2">
+        <v>20</v>
+      </c>
+      <c r="P25">
+        <v>25</v>
+      </c>
+      <c r="Q25">
+        <v>35</v>
+      </c>
+      <c r="R25" s="2">
+        <v>20</v>
+      </c>
+      <c r="S25" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T25" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U25" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="V25" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W25" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X25" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA25" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>5</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26">
+        <v>0.3</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>105</v>
+      </c>
+      <c r="J26">
+        <v>90</v>
+      </c>
+      <c r="K26">
+        <v>180</v>
+      </c>
+      <c r="L26">
+        <v>0.4</v>
+      </c>
+      <c r="M26">
+        <v>0.6</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2">
+        <v>20</v>
+      </c>
+      <c r="P26">
+        <v>25</v>
+      </c>
+      <c r="Q26">
+        <v>35</v>
+      </c>
+      <c r="R26" s="2">
+        <v>20</v>
+      </c>
+      <c r="S26" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T26" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U26" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="V26" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W26" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X26" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>5</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27">
+        <v>0.3</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>120</v>
+      </c>
+      <c r="J27">
+        <v>90</v>
+      </c>
+      <c r="K27">
+        <v>180</v>
+      </c>
+      <c r="L27">
+        <v>0.4</v>
+      </c>
+      <c r="M27">
+        <v>0.6</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2">
+        <v>20</v>
+      </c>
+      <c r="P27">
+        <v>25</v>
+      </c>
+      <c r="Q27">
+        <v>35</v>
+      </c>
+      <c r="R27" s="2">
+        <v>20</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T27" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U27" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="V27" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W27" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X27" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z27" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>5</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28">
+        <v>0.3</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>135</v>
+      </c>
+      <c r="J28">
+        <v>90</v>
+      </c>
+      <c r="K28">
+        <v>180</v>
+      </c>
+      <c r="L28">
+        <v>0.4</v>
+      </c>
+      <c r="M28">
+        <v>0.6</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2">
+        <v>20</v>
+      </c>
+      <c r="P28">
+        <v>25</v>
+      </c>
+      <c r="Q28">
+        <v>35</v>
+      </c>
+      <c r="R28" s="2">
+        <v>20</v>
+      </c>
+      <c r="S28" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T28" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="V28" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W28" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X28" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="Y28" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z28" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA28" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>5</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29">
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>150</v>
+      </c>
+      <c r="J29">
+        <v>90</v>
+      </c>
+      <c r="K29">
+        <v>180</v>
+      </c>
+      <c r="L29">
+        <v>0.4</v>
+      </c>
+      <c r="M29">
+        <v>0.6</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2">
+        <v>20</v>
+      </c>
+      <c r="P29">
+        <v>25</v>
+      </c>
+      <c r="Q29">
+        <v>35</v>
+      </c>
+      <c r="R29" s="2">
+        <v>20</v>
+      </c>
+      <c r="S29" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T29" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U29" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="V29" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W29" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X29" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="Y29" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z29" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA29" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>5</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30">
+        <v>0.3</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>165</v>
+      </c>
+      <c r="J30">
+        <v>90</v>
+      </c>
+      <c r="K30">
+        <v>180</v>
+      </c>
+      <c r="L30">
+        <v>0.4</v>
+      </c>
+      <c r="M30">
+        <v>0.6</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2">
+        <v>20</v>
+      </c>
+      <c r="P30">
+        <v>25</v>
+      </c>
+      <c r="Q30">
+        <v>35</v>
+      </c>
+      <c r="R30" s="2">
+        <v>20</v>
+      </c>
+      <c r="S30" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T30" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U30" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="V30" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W30" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X30" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="Y30" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z30" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA30" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>5</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31">
+        <v>0.3</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>180</v>
+      </c>
+      <c r="J31">
+        <v>90</v>
+      </c>
+      <c r="K31">
+        <v>180</v>
+      </c>
+      <c r="L31">
+        <v>0.4</v>
+      </c>
+      <c r="M31">
+        <v>0.6</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31" s="2">
+        <v>20</v>
+      </c>
+      <c r="P31">
+        <v>25</v>
+      </c>
+      <c r="Q31">
+        <v>35</v>
+      </c>
+      <c r="R31" s="2">
+        <v>20</v>
+      </c>
+      <c r="S31" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T31" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U31" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="V31" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W31" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X31" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="Y31" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z31" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA31" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>5</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6E57C8-E44E-0D40-94F9-4930F2CD4737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEABE94-B938-2048-BCF5-9FB20227315E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="10000" windowHeight="16340" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="10000" windowHeight="17980" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="89">
   <si>
     <t>winter_barley_59</t>
   </si>
@@ -249,6 +249,60 @@
   </si>
   <si>
     <t>white_potato_141</t>
+  </si>
+  <si>
+    <t>spring_oat_128</t>
+  </si>
+  <si>
+    <t>spring_oat_129</t>
+  </si>
+  <si>
+    <t>spring_oat_130</t>
+  </si>
+  <si>
+    <t>dry_pea_189</t>
+  </si>
+  <si>
+    <t>dry_pea_191</t>
+  </si>
+  <si>
+    <t>dry_pea_190</t>
+  </si>
+  <si>
+    <t>winter_rape_216</t>
+  </si>
+  <si>
+    <t>winter_rape_217</t>
+  </si>
+  <si>
+    <t>winter_rape_218</t>
+  </si>
+  <si>
+    <t>winter_rape_219</t>
+  </si>
+  <si>
+    <t>spring_rape_220</t>
+  </si>
+  <si>
+    <t>spring_rape_221</t>
+  </si>
+  <si>
+    <t>spring_rape_222</t>
+  </si>
+  <si>
+    <t>spring_rape_223</t>
+  </si>
+  <si>
+    <t>rabi_rape_224</t>
+  </si>
+  <si>
+    <t>rabi_rape_225</t>
+  </si>
+  <si>
+    <t>alfalfa_291</t>
+  </si>
+  <si>
+    <t>alfalfa_292</t>
   </si>
 </sst>
 </file>
@@ -641,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9258CFFF-D0F8-3E49-9200-AC8FAB870EFD}">
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -795,7 +849,7 @@
         <v>140</v>
       </c>
       <c r="J2">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="K2">
         <v>240</v>
@@ -914,7 +968,7 @@
         <v>160</v>
       </c>
       <c r="J3">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="K3">
         <v>240</v>
@@ -1033,7 +1087,7 @@
         <v>180</v>
       </c>
       <c r="J4">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="K4">
         <v>240</v>
@@ -1152,7 +1206,7 @@
         <v>200</v>
       </c>
       <c r="J5">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="K5">
         <v>240</v>
@@ -1274,7 +1328,7 @@
         <v>90</v>
       </c>
       <c r="K6">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1393,7 +1447,7 @@
         <v>90</v>
       </c>
       <c r="K7">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -1512,7 +1566,7 @@
         <v>90</v>
       </c>
       <c r="K8">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -1631,7 +1685,7 @@
         <v>90</v>
       </c>
       <c r="K9">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -1747,10 +1801,10 @@
         <v>140</v>
       </c>
       <c r="J10">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="K10">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L10">
         <v>1.5</v>
@@ -1866,10 +1920,10 @@
         <v>160</v>
       </c>
       <c r="J11">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="K11">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L11">
         <v>1.5</v>
@@ -1985,10 +2039,10 @@
         <v>180</v>
       </c>
       <c r="J12">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="K12">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L12">
         <v>1.5</v>
@@ -2104,10 +2158,10 @@
         <v>200</v>
       </c>
       <c r="J13">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="K13">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L13">
         <v>1.5</v>
@@ -2226,7 +2280,7 @@
         <v>90</v>
       </c>
       <c r="K14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -2345,7 +2399,7 @@
         <v>90</v>
       </c>
       <c r="K15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -2464,7 +2518,7 @@
         <v>90</v>
       </c>
       <c r="K16">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L16">
         <v>1</v>
@@ -2583,7 +2637,7 @@
         <v>90</v>
       </c>
       <c r="K17">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L17">
         <v>1</v>
@@ -2702,7 +2756,7 @@
         <v>90</v>
       </c>
       <c r="K18">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -2806,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2925,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3044,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3163,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3282,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3401,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4333,6 +4387,1446 @@
         <v>39</v>
       </c>
       <c r="AM31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32">
+        <v>0.15</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>90</v>
+      </c>
+      <c r="J32">
+        <v>110</v>
+      </c>
+      <c r="K32">
+        <v>160</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>1.5</v>
+      </c>
+      <c r="N32">
+        <v>1.2</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>5</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33">
+        <v>0.15</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>105</v>
+      </c>
+      <c r="J33">
+        <v>110</v>
+      </c>
+      <c r="K33">
+        <v>160</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1.5</v>
+      </c>
+      <c r="N33">
+        <v>1.2</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>5</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34">
+        <v>0.15</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>120</v>
+      </c>
+      <c r="J34">
+        <v>110</v>
+      </c>
+      <c r="K34">
+        <v>160</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>1.5</v>
+      </c>
+      <c r="N34">
+        <v>1.2</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>5</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35">
+        <v>0.15</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>90</v>
+      </c>
+      <c r="J35">
+        <v>85</v>
+      </c>
+      <c r="K35">
+        <v>140</v>
+      </c>
+      <c r="L35">
+        <v>0.6</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>3</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>5</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36">
+        <v>0.15</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>105</v>
+      </c>
+      <c r="J36">
+        <v>85</v>
+      </c>
+      <c r="K36">
+        <v>140</v>
+      </c>
+      <c r="L36">
+        <v>0.6</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>5</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37">
+        <v>0.15</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>120</v>
+      </c>
+      <c r="J37">
+        <v>85</v>
+      </c>
+      <c r="K37">
+        <v>140</v>
+      </c>
+      <c r="L37">
+        <v>0.6</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>3</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>5</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D38">
+        <v>1.5</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>35</v>
+      </c>
+      <c r="H38">
+        <v>105</v>
+      </c>
+      <c r="I38">
+        <v>140</v>
+      </c>
+      <c r="J38">
+        <v>160</v>
+      </c>
+      <c r="K38">
+        <v>340</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>1.5</v>
+      </c>
+      <c r="N38">
+        <v>2</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>5</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>40</v>
+      </c>
+      <c r="H39">
+        <v>120</v>
+      </c>
+      <c r="I39">
+        <v>160</v>
+      </c>
+      <c r="J39">
+        <v>160</v>
+      </c>
+      <c r="K39">
+        <v>340</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>1.5</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>5</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>45</v>
+      </c>
+      <c r="H40">
+        <v>135</v>
+      </c>
+      <c r="I40">
+        <v>180</v>
+      </c>
+      <c r="J40">
+        <v>160</v>
+      </c>
+      <c r="K40">
+        <v>340</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>1.5</v>
+      </c>
+      <c r="N40">
+        <v>2</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>5</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>45</v>
+      </c>
+      <c r="H41">
+        <v>150</v>
+      </c>
+      <c r="I41">
+        <v>195</v>
+      </c>
+      <c r="J41">
+        <v>160</v>
+      </c>
+      <c r="K41">
+        <v>340</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>1.5</v>
+      </c>
+      <c r="N41">
+        <v>2</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>5</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D42">
+        <v>1.5</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>105</v>
+      </c>
+      <c r="J42">
+        <v>85</v>
+      </c>
+      <c r="K42">
+        <v>160</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>1.5</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>5</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D43">
+        <v>1.5</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>120</v>
+      </c>
+      <c r="J43">
+        <v>85</v>
+      </c>
+      <c r="K43">
+        <v>160</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>1.5</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>5</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM43" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D44">
+        <v>1.5</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>135</v>
+      </c>
+      <c r="J44">
+        <v>85</v>
+      </c>
+      <c r="K44">
+        <v>160</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>1.5</v>
+      </c>
+      <c r="N44">
+        <v>2</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>5</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>150</v>
+      </c>
+      <c r="J45">
+        <v>85</v>
+      </c>
+      <c r="K45">
+        <v>160</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>1.5</v>
+      </c>
+      <c r="N45">
+        <v>2</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>5</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D46">
+        <v>1.5</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>135</v>
+      </c>
+      <c r="J46">
+        <v>85</v>
+      </c>
+      <c r="K46">
+        <v>340</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46">
+        <v>1.5</v>
+      </c>
+      <c r="N46">
+        <v>2</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>5</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>150</v>
+      </c>
+      <c r="J47">
+        <v>85</v>
+      </c>
+      <c r="K47">
+        <v>340</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>1.5</v>
+      </c>
+      <c r="N47">
+        <v>2</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>5</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>360</v>
+      </c>
+      <c r="J48">
+        <v>100</v>
+      </c>
+      <c r="K48">
+        <v>365</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48">
+        <v>2</v>
+      </c>
+      <c r="N48">
+        <v>0.9</v>
+      </c>
+      <c r="AB48">
+        <v>1</v>
+      </c>
+      <c r="AC48">
+        <v>5</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM48" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>360</v>
+      </c>
+      <c r="J49">
+        <v>100</v>
+      </c>
+      <c r="K49">
+        <v>365</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49">
+        <v>2</v>
+      </c>
+      <c r="N49">
+        <v>0.9</v>
+      </c>
+      <c r="AB49">
+        <v>1</v>
+      </c>
+      <c r="AC49">
+        <v>10</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM49" t="s">
         <v>39</v>
       </c>
     </row>

--- a/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEABE94-B938-2048-BCF5-9FB20227315E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9138EF93-EDEC-2F44-A7CE-D3A6C7C8C5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="10000" windowHeight="17980" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="85">
   <si>
     <t>winter_barley_59</t>
   </si>
@@ -291,18 +291,6 @@
   </si>
   <si>
     <t>spring_rape_223</t>
-  </si>
-  <si>
-    <t>rabi_rape_224</t>
-  </si>
-  <si>
-    <t>rabi_rape_225</t>
-  </si>
-  <si>
-    <t>alfalfa_291</t>
-  </si>
-  <si>
-    <t>alfalfa_292</t>
   </si>
 </sst>
 </file>
@@ -695,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9258CFFF-D0F8-3E49-9200-AC8FAB870EFD}">
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AM45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -4433,6 +4421,45 @@
       <c r="N32">
         <v>1.2</v>
       </c>
+      <c r="O32" s="2">
+        <v>15</v>
+      </c>
+      <c r="P32">
+        <v>25</v>
+      </c>
+      <c r="Q32">
+        <v>40</v>
+      </c>
+      <c r="R32" s="2">
+        <v>20</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T32" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U32" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="V32" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W32" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X32" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z32" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA32" s="2">
+        <v>1.1499999999999999</v>
+      </c>
       <c r="AB32">
         <v>0</v>
       </c>
@@ -4513,6 +4540,45 @@
       <c r="N33">
         <v>1.2</v>
       </c>
+      <c r="O33" s="2">
+        <v>15</v>
+      </c>
+      <c r="P33">
+        <v>25</v>
+      </c>
+      <c r="Q33">
+        <v>40</v>
+      </c>
+      <c r="R33" s="2">
+        <v>20</v>
+      </c>
+      <c r="S33" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T33" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U33" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="V33" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W33" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X33" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y33" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z33" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA33" s="2">
+        <v>1.1499999999999999</v>
+      </c>
       <c r="AB33">
         <v>0</v>
       </c>
@@ -4593,6 +4659,45 @@
       <c r="N34">
         <v>1.2</v>
       </c>
+      <c r="O34" s="2">
+        <v>15</v>
+      </c>
+      <c r="P34">
+        <v>25</v>
+      </c>
+      <c r="Q34">
+        <v>40</v>
+      </c>
+      <c r="R34" s="2">
+        <v>20</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T34" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U34" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="V34" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="W34" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X34" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y34" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Z34" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA34" s="2">
+        <v>1.1499999999999999</v>
+      </c>
       <c r="AB34">
         <v>0</v>
       </c>
@@ -4673,6 +4778,45 @@
       <c r="N35">
         <v>3</v>
       </c>
+      <c r="O35" s="2">
+        <v>20</v>
+      </c>
+      <c r="P35">
+        <v>30</v>
+      </c>
+      <c r="Q35">
+        <v>35</v>
+      </c>
+      <c r="R35" s="2">
+        <v>15</v>
+      </c>
+      <c r="S35" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T35" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U35" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V35" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W35" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X35" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y35" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Z35" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="AB35">
         <v>0</v>
       </c>
@@ -4753,6 +4897,45 @@
       <c r="N36">
         <v>3</v>
       </c>
+      <c r="O36" s="2">
+        <v>20</v>
+      </c>
+      <c r="P36">
+        <v>30</v>
+      </c>
+      <c r="Q36">
+        <v>35</v>
+      </c>
+      <c r="R36" s="2">
+        <v>15</v>
+      </c>
+      <c r="S36" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T36" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U36" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V36" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W36" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X36" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y36" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Z36" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA36" s="2">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="AB36">
         <v>0</v>
       </c>
@@ -4833,6 +5016,45 @@
       <c r="N37">
         <v>3</v>
       </c>
+      <c r="O37" s="2">
+        <v>20</v>
+      </c>
+      <c r="P37">
+        <v>30</v>
+      </c>
+      <c r="Q37">
+        <v>35</v>
+      </c>
+      <c r="R37" s="2">
+        <v>15</v>
+      </c>
+      <c r="S37" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T37" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U37" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V37" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W37" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X37" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y37" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Z37" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA37" s="2">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="AB37">
         <v>0</v>
       </c>
@@ -4913,6 +5135,45 @@
       <c r="N38">
         <v>2</v>
       </c>
+      <c r="O38" s="2">
+        <v>10</v>
+      </c>
+      <c r="P38">
+        <v>30</v>
+      </c>
+      <c r="Q38">
+        <v>40</v>
+      </c>
+      <c r="R38" s="2">
+        <v>20</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T38" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="U38" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="V38" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W38" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X38" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y38" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Z38" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA38" s="2">
+        <v>0.85</v>
+      </c>
       <c r="AB38">
         <v>0</v>
       </c>
@@ -4993,6 +5254,45 @@
       <c r="N39">
         <v>2</v>
       </c>
+      <c r="O39" s="2">
+        <v>10</v>
+      </c>
+      <c r="P39">
+        <v>30</v>
+      </c>
+      <c r="Q39">
+        <v>40</v>
+      </c>
+      <c r="R39" s="2">
+        <v>20</v>
+      </c>
+      <c r="S39" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T39" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="U39" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="V39" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W39" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X39" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y39" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Z39" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA39" s="2">
+        <v>0.85</v>
+      </c>
       <c r="AB39">
         <v>0</v>
       </c>
@@ -5073,6 +5373,45 @@
       <c r="N40">
         <v>2</v>
       </c>
+      <c r="O40" s="2">
+        <v>10</v>
+      </c>
+      <c r="P40">
+        <v>30</v>
+      </c>
+      <c r="Q40">
+        <v>40</v>
+      </c>
+      <c r="R40" s="2">
+        <v>20</v>
+      </c>
+      <c r="S40" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T40" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="U40" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="V40" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W40" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X40" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y40" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Z40" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA40" s="2">
+        <v>0.85</v>
+      </c>
       <c r="AB40">
         <v>0</v>
       </c>
@@ -5153,6 +5492,45 @@
       <c r="N41">
         <v>2</v>
       </c>
+      <c r="O41" s="2">
+        <v>10</v>
+      </c>
+      <c r="P41">
+        <v>30</v>
+      </c>
+      <c r="Q41">
+        <v>40</v>
+      </c>
+      <c r="R41" s="2">
+        <v>20</v>
+      </c>
+      <c r="S41" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T41" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="U41" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="V41" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y41" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Z41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA41" s="2">
+        <v>0.85</v>
+      </c>
       <c r="AB41">
         <v>0</v>
       </c>
@@ -5233,6 +5611,45 @@
       <c r="N42">
         <v>2</v>
       </c>
+      <c r="O42" s="2">
+        <v>10</v>
+      </c>
+      <c r="P42">
+        <v>30</v>
+      </c>
+      <c r="Q42">
+        <v>40</v>
+      </c>
+      <c r="R42" s="2">
+        <v>20</v>
+      </c>
+      <c r="S42" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T42" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="U42" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="V42" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W42" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X42" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y42" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Z42" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA42" s="2">
+        <v>0.85</v>
+      </c>
       <c r="AB42">
         <v>0</v>
       </c>
@@ -5313,6 +5730,45 @@
       <c r="N43">
         <v>2</v>
       </c>
+      <c r="O43" s="2">
+        <v>10</v>
+      </c>
+      <c r="P43">
+        <v>30</v>
+      </c>
+      <c r="Q43">
+        <v>40</v>
+      </c>
+      <c r="R43" s="2">
+        <v>20</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T43" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="U43" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="V43" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W43" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X43" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y43" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Z43" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>0.85</v>
+      </c>
       <c r="AB43">
         <v>0</v>
       </c>
@@ -5393,6 +5849,45 @@
       <c r="N44">
         <v>2</v>
       </c>
+      <c r="O44" s="2">
+        <v>10</v>
+      </c>
+      <c r="P44">
+        <v>30</v>
+      </c>
+      <c r="Q44">
+        <v>40</v>
+      </c>
+      <c r="R44" s="2">
+        <v>20</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T44" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="U44" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="V44" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W44" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X44" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y44" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Z44" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA44" s="2">
+        <v>0.85</v>
+      </c>
       <c r="AB44">
         <v>0</v>
       </c>
@@ -5473,6 +5968,45 @@
       <c r="N45">
         <v>2</v>
       </c>
+      <c r="O45" s="2">
+        <v>10</v>
+      </c>
+      <c r="P45">
+        <v>30</v>
+      </c>
+      <c r="Q45">
+        <v>40</v>
+      </c>
+      <c r="R45" s="2">
+        <v>20</v>
+      </c>
+      <c r="S45" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T45" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="U45" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="V45" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W45" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="X45" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Y45" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Z45" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA45" s="2">
+        <v>0.85</v>
+      </c>
       <c r="AB45">
         <v>0</v>
       </c>
@@ -5507,326 +6041,6 @@
         <v>39</v>
       </c>
       <c r="AM45" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="D46">
-        <v>1.5</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>135</v>
-      </c>
-      <c r="J46">
-        <v>85</v>
-      </c>
-      <c r="K46">
-        <v>340</v>
-      </c>
-      <c r="L46">
-        <v>1</v>
-      </c>
-      <c r="M46">
-        <v>1.5</v>
-      </c>
-      <c r="N46">
-        <v>2</v>
-      </c>
-      <c r="AB46">
-        <v>0</v>
-      </c>
-      <c r="AC46">
-        <v>5</v>
-      </c>
-      <c r="AD46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM46" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" t="s">
-        <v>38</v>
-      </c>
-      <c r="C47" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="D47">
-        <v>2</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>150</v>
-      </c>
-      <c r="J47">
-        <v>85</v>
-      </c>
-      <c r="K47">
-        <v>340</v>
-      </c>
-      <c r="L47">
-        <v>1</v>
-      </c>
-      <c r="M47">
-        <v>1.5</v>
-      </c>
-      <c r="N47">
-        <v>2</v>
-      </c>
-      <c r="AB47">
-        <v>0</v>
-      </c>
-      <c r="AC47">
-        <v>5</v>
-      </c>
-      <c r="AD47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM47" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" t="s">
-        <v>38</v>
-      </c>
-      <c r="C48" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="D48">
-        <v>3</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>360</v>
-      </c>
-      <c r="J48">
-        <v>100</v>
-      </c>
-      <c r="K48">
-        <v>365</v>
-      </c>
-      <c r="L48">
-        <v>1</v>
-      </c>
-      <c r="M48">
-        <v>2</v>
-      </c>
-      <c r="N48">
-        <v>0.9</v>
-      </c>
-      <c r="AB48">
-        <v>1</v>
-      </c>
-      <c r="AC48">
-        <v>5</v>
-      </c>
-      <c r="AD48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM48" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" t="s">
-        <v>38</v>
-      </c>
-      <c r="C49" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="D49">
-        <v>3</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>360</v>
-      </c>
-      <c r="J49">
-        <v>100</v>
-      </c>
-      <c r="K49">
-        <v>365</v>
-      </c>
-      <c r="L49">
-        <v>1</v>
-      </c>
-      <c r="M49">
-        <v>2</v>
-      </c>
-      <c r="N49">
-        <v>0.9</v>
-      </c>
-      <c r="AB49">
-        <v>1</v>
-      </c>
-      <c r="AC49">
-        <v>10</v>
-      </c>
-      <c r="AD49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM49" t="s">
         <v>39</v>
       </c>
     </row>
